--- a/Práctica Parcial/data/DiccionarioDatosEstudiantes.xlsx
+++ b/Práctica Parcial/data/DiccionarioDatosEstudiantes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes-my.sharepoint.com/personal/mavillam_uniandes_edu_co/Documents/Documentos/cursos/InteligenciaDeNegocios/2025_20/Parciales/Parcial1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mattia/Library/Mobile Documents/com~apple~CloudDocs/UNIANDES/git/MaterialDeClase-ISIS-2611-1/Práctica Parcial/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{7512B9D5-F57C-48C4-B5F2-4D694C42C02C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{216E3E56-F9A0-45DF-86AA-136C5FBFE978}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A8F76C-948F-C245-BE09-50FF587FE788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11265" windowHeight="2280" xr2:uid="{0DA9D8D8-3FE7-4803-9C01-29D8F2A1624F}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="12680" windowHeight="17100" xr2:uid="{0DA9D8D8-3FE7-4803-9C01-29D8F2A1624F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -265,9 +265,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -305,7 +305,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -411,7 +411,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -553,7 +553,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -562,13 +562,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED8DA773-E1B8-4394-892E-AFF5915F147D}">
   <dimension ref="B1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.1640625" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
@@ -576,7 +576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -584,7 +584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
@@ -592,7 +592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>31</v>
       </c>
@@ -600,7 +600,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
@@ -608,7 +608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:3" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
@@ -616,7 +616,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:3" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
@@ -624,7 +624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
@@ -632,7 +632,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
@@ -640,7 +640,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
@@ -648,7 +648,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
@@ -656,7 +656,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>17</v>
       </c>
@@ -664,7 +664,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
@@ -672,7 +672,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:3" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:3" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>23</v>
       </c>
@@ -688,7 +688,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>25</v>
       </c>
@@ -696,7 +696,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>27</v>
       </c>
@@ -704,7 +704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>34</v>
       </c>
@@ -712,7 +712,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>36</v>
       </c>
@@ -727,6 +727,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="e393c52d-5107-4f8c-8de8-eae10f17b749" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CA0D6A37D0C0054880D4AFE635237E97" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="78ca05fa4facb2c1fee30260b5e386ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="e393c52d-5107-4f8c-8de8-eae10f17b749" xmlns:ns4="33836db8-7ef1-4162-bc08-4d3d268287a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5d4c2edead0161c683c8af9e8113e91e" ns3:_="" ns4:_="">
     <xsd:import namespace="e393c52d-5107-4f8c-8de8-eae10f17b749"/>
@@ -971,24 +988,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D20BBECF-0574-4891-AF7A-DBF1BCEE76E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="e393c52d-5107-4f8c-8de8-eae10f17b749"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="33836db8-7ef1-4162-bc08-4d3d268287a0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="e393c52d-5107-4f8c-8de8-eae10f17b749" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9E03034-D35A-4BDF-97D7-6DAEE610E0FB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34B20474-38CF-4739-8EAD-1D7E9E70EB89}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1005,29 +1030,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9E03034-D35A-4BDF-97D7-6DAEE610E0FB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D20BBECF-0574-4891-AF7A-DBF1BCEE76E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="e393c52d-5107-4f8c-8de8-eae10f17b749"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="33836db8-7ef1-4162-bc08-4d3d268287a0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>